--- a/TestData/TestReport.xlsx
+++ b/TestData/TestReport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="53">
   <si>
     <t>S.No</t>
   </si>
@@ -59,7 +59,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>verifyChartVisible</t>
+    <t>verifyPieChartVisible</t>
   </si>
   <si>
     <t>6</t>
@@ -149,25 +149,28 @@
     <t>19</t>
   </si>
   <si>
+    <t>writePersonalLoanDataToExcel</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>HomeLoanPageTest</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
     <t>writeHomeLoanDataToExcel</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>HomeLoanPageTest</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
   </si>
 </sst>
 </file>
@@ -565,7 +568,7 @@
         <v>47</v>
       </c>
       <c r="C25" t="s" s="0">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s" s="0">
         <v>7</v>
